--- a/tests/antares/resources/expected_output_files/specific_2035.xlsx
+++ b/tests/antares/resources/expected_output_files/specific_2035.xlsx
@@ -1245,7 +1245,7 @@
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
-        <v>0.6964231738035265</v>
+        <v>0.9928463476070529</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -1274,7 +1274,7 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R7" t="n">
         <v>0.05</v>
@@ -2197,13 +2197,13 @@
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="n">
-        <v>0.5816207373737983</v>
+        <v>0.7224014393556351</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>0.4199882857905282</v>
+        <v>0.4211119334433324</v>
       </c>
       <c r="I15" t="n">
         <v>0.08000000000000002</v>
@@ -2212,7 +2212,7 @@
         <v>1</v>
       </c>
       <c r="K15" t="n">
-        <v>27</v>
+        <v>27.00000000000001</v>
       </c>
       <c r="L15" t="n">
         <v>0.15</v>
@@ -2226,7 +2226,7 @@
         <v>1</v>
       </c>
       <c r="Q15" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="R15" t="n">
         <v>0.08000000000000002</v>
@@ -2265,13 +2265,13 @@
         <v>0.08000000000000002</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.02225274725274724</v>
+        <v>0.02225274725274726</v>
       </c>
       <c r="AE15" t="n">
-        <v>0.02225274725274724</v>
+        <v>0.02225274725274726</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.02225274725274724</v>
+        <v>0.02225274725274726</v>
       </c>
       <c r="AG15" t="n">
         <v>0.1254098360655738</v>
@@ -2292,13 +2292,13 @@
         <v>0.1254098360655738</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.02225274725274724</v>
+        <v>0.02225274725274726</v>
       </c>
       <c r="AN15" t="n">
-        <v>0.02225274725274724</v>
+        <v>0.02225274725274726</v>
       </c>
       <c r="AO15" t="n">
-        <v>0.02225274725274724</v>
+        <v>0.02225274725274726</v>
       </c>
     </row>
     <row r="16">
@@ -2673,7 +2673,7 @@
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="n">
-        <v>0.6875</v>
+        <v>1.375</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -2702,7 +2702,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R19" t="n">
         <v>0.05</v>
@@ -2792,16 +2792,16 @@
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="n">
-        <v>0.7485714285714286</v>
+        <v>1.624761904761905</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0.4569482288828338</v>
+        <v>0.3998729351969504</v>
       </c>
       <c r="I20" t="n">
-        <v>0.06716621253405994</v>
+        <v>0.07401524777636595</v>
       </c>
       <c r="J20" t="n">
         <v>1</v>
@@ -2810,7 +2810,7 @@
         <v>27</v>
       </c>
       <c r="L20" t="n">
-        <v>0.06416893732970028</v>
+        <v>0.02992376111817027</v>
       </c>
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
@@ -2821,79 +2821,79 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R20" t="n">
-        <v>0.06716621253405994</v>
+        <v>0.07401524777636595</v>
       </c>
       <c r="S20" t="n">
-        <v>0.06716621253405994</v>
+        <v>0.07401524777636595</v>
       </c>
       <c r="T20" t="n">
-        <v>0.06716621253405994</v>
+        <v>0.07401524777636595</v>
       </c>
       <c r="U20" t="n">
-        <v>0.06716621253405994</v>
+        <v>0.07401524777636595</v>
       </c>
       <c r="V20" t="n">
-        <v>0.06716621253405994</v>
+        <v>0.07401524777636595</v>
       </c>
       <c r="W20" t="n">
-        <v>0.06716621253405994</v>
+        <v>0.07401524777636595</v>
       </c>
       <c r="X20" t="n">
-        <v>0.06716621253405994</v>
+        <v>0.07401524777636595</v>
       </c>
       <c r="Y20" t="n">
-        <v>0.06716621253405994</v>
+        <v>0.07401524777636595</v>
       </c>
       <c r="Z20" t="n">
-        <v>0.06716621253405994</v>
+        <v>0.07401524777636595</v>
       </c>
       <c r="AA20" t="n">
-        <v>0.06716621253405994</v>
+        <v>0.07401524777636595</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.06716621253405994</v>
+        <v>0.07401524777636595</v>
       </c>
       <c r="AC20" t="n">
-        <v>0.06716621253405994</v>
+        <v>0.07401524777636595</v>
       </c>
       <c r="AD20" t="n">
-        <v>0.009519567625834656</v>
+        <v>0.004439239286761524</v>
       </c>
       <c r="AE20" t="n">
-        <v>0.009519567625834656</v>
+        <v>0.004439239286761524</v>
       </c>
       <c r="AF20" t="n">
-        <v>0.009519567625834656</v>
+        <v>0.004439239286761524</v>
       </c>
       <c r="AG20" t="n">
-        <v>0.1380734354759459</v>
+        <v>0.1431260024579749</v>
       </c>
       <c r="AH20" t="n">
-        <v>0.1380734354759459</v>
+        <v>0.1431260024579749</v>
       </c>
       <c r="AI20" t="n">
-        <v>0.1380734354759459</v>
+        <v>0.1431260024579749</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0.1380734354759459</v>
+        <v>0.1431260024579749</v>
       </c>
       <c r="AK20" t="n">
-        <v>0.1380734354759459</v>
+        <v>0.1431260024579749</v>
       </c>
       <c r="AL20" t="n">
-        <v>0.1380734354759459</v>
+        <v>0.1431260024579749</v>
       </c>
       <c r="AM20" t="n">
-        <v>0.009519567625834656</v>
+        <v>0.004439239286761524</v>
       </c>
       <c r="AN20" t="n">
-        <v>0.009519567625834656</v>
+        <v>0.004439239286761524</v>
       </c>
       <c r="AO20" t="n">
-        <v>0.009519567625834656</v>
+        <v>0.004439239286761524</v>
       </c>
     </row>
     <row r="21">
@@ -3982,7 +3982,7 @@
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="n">
-        <v>0.5121478270788182</v>
+        <v>1.536443481236455</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -4011,7 +4011,7 @@
         <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R30" t="n">
         <v>0.05</v>
@@ -4050,13 +4050,13 @@
         <v>0.05</v>
       </c>
       <c r="AD30" t="n">
-        <v>0.02225274725274725</v>
+        <v>0.02225274725274726</v>
       </c>
       <c r="AE30" t="n">
-        <v>0.02225274725274725</v>
+        <v>0.02225274725274726</v>
       </c>
       <c r="AF30" t="n">
-        <v>0.02225274725274725</v>
+        <v>0.02225274725274726</v>
       </c>
       <c r="AG30" t="n">
         <v>0.1254098360655738</v>
@@ -4077,13 +4077,13 @@
         <v>0.1254098360655738</v>
       </c>
       <c r="AM30" t="n">
-        <v>0.02225274725274725</v>
+        <v>0.02225274725274726</v>
       </c>
       <c r="AN30" t="n">
-        <v>0.02225274725274725</v>
+        <v>0.02225274725274726</v>
       </c>
       <c r="AO30" t="n">
-        <v>0.02225274725274725</v>
+        <v>0.02225274725274726</v>
       </c>
     </row>
     <row r="31">
@@ -4101,7 +4101,7 @@
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="n">
-        <v>1.354243542435424</v>
+        <v>2.708487084870849</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -4130,7 +4130,7 @@
         <v>1</v>
       </c>
       <c r="Q31" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R31" t="n">
         <v>0.098</v>
@@ -4339,7 +4339,7 @@
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="n">
-        <v>0.4017216642754661</v>
+        <v>0.8034433285509323</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -4368,7 +4368,7 @@
         <v>1</v>
       </c>
       <c r="Q33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R33" t="n">
         <v>0.08</v>
@@ -4458,7 +4458,7 @@
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="n">
-        <v>1.693251533742331</v>
+        <v>5.079754601226994</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -4487,7 +4487,7 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="R34" t="n">
         <v>0.11</v>
@@ -4696,7 +4696,7 @@
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="n">
-        <v>1.147892783505155</v>
+        <v>1.353039175257732</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -4705,7 +4705,7 @@
         <v>0.5999999999999999</v>
       </c>
       <c r="I36" t="n">
-        <v>0.05</v>
+        <v>0.05000000000000001</v>
       </c>
       <c r="J36" t="n">
         <v>1</v>
@@ -4725,43 +4725,43 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="R36" t="n">
-        <v>0.05</v>
+        <v>0.05000000000000001</v>
       </c>
       <c r="S36" t="n">
-        <v>0.05</v>
+        <v>0.05000000000000001</v>
       </c>
       <c r="T36" t="n">
-        <v>0.05</v>
+        <v>0.05000000000000001</v>
       </c>
       <c r="U36" t="n">
-        <v>0.05</v>
+        <v>0.05000000000000001</v>
       </c>
       <c r="V36" t="n">
-        <v>0.05</v>
+        <v>0.05000000000000001</v>
       </c>
       <c r="W36" t="n">
-        <v>0.05</v>
+        <v>0.05000000000000001</v>
       </c>
       <c r="X36" t="n">
-        <v>0.05</v>
+        <v>0.05000000000000001</v>
       </c>
       <c r="Y36" t="n">
-        <v>0.05</v>
+        <v>0.05000000000000001</v>
       </c>
       <c r="Z36" t="n">
-        <v>0.05</v>
+        <v>0.05000000000000001</v>
       </c>
       <c r="AA36" t="n">
-        <v>0.05</v>
+        <v>0.05000000000000001</v>
       </c>
       <c r="AB36" t="n">
-        <v>0.05</v>
+        <v>0.05000000000000001</v>
       </c>
       <c r="AC36" t="n">
-        <v>0.05</v>
+        <v>0.05000000000000001</v>
       </c>
       <c r="AD36" t="n">
         <v>0.02225274725274725</v>
@@ -4934,13 +4934,13 @@
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="n">
-        <v>0.9364548494983277</v>
+        <v>1.438127090301003</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>0.5599999999999999</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I38" t="n">
         <v>0.05</v>
@@ -4963,7 +4963,7 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R38" t="n">
         <v>0.05</v>
@@ -5178,7 +5178,7 @@
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>0.3300000000000001</v>
+        <v>0.33</v>
       </c>
       <c r="I40" t="n">
         <v>0.05</v>
@@ -5410,22 +5410,22 @@
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="n">
-        <v>7.576310160427806</v>
+        <v>8.885294117647058</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>0.5682460699345954</v>
+        <v>0.5712067751753341</v>
       </c>
       <c r="I42" t="n">
         <v>0.04730000000000002</v>
       </c>
       <c r="J42" t="n">
-        <v>3.67</v>
+        <v>3.670000000000001</v>
       </c>
       <c r="K42" t="n">
-        <v>70.00000000000001</v>
+        <v>70</v>
       </c>
       <c r="L42" t="n">
         <v>0.4600000000000001</v>
@@ -5439,7 +5439,7 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>107</v>
+        <v>127</v>
       </c>
       <c r="R42" t="n">
         <v>0.04730000000000002</v>
@@ -5529,7 +5529,7 @@
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="n">
-        <v>1.953358288770054</v>
+        <v>1.978171122994652</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -5541,7 +5541,7 @@
         <v>0.04730000000000002</v>
       </c>
       <c r="J43" t="n">
-        <v>3.67</v>
+        <v>3.670000000000001</v>
       </c>
       <c r="K43" t="n">
         <v>70.00000000000001</v>
@@ -5558,7 +5558,7 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="R43" t="n">
         <v>0.04730000000000002</v>
@@ -5886,22 +5886,22 @@
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="n">
-        <v>3.249595141700405</v>
+        <v>3.426720647773279</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>0.5500000000000002</v>
+        <v>0.55</v>
       </c>
       <c r="I46" t="n">
-        <v>0.04730000000000001</v>
+        <v>0.0473</v>
       </c>
       <c r="J46" t="n">
         <v>3.670000000000001</v>
       </c>
       <c r="K46" t="n">
-        <v>70</v>
+        <v>69.99999999999999</v>
       </c>
       <c r="L46" t="n">
         <v>0.46</v>
@@ -5915,43 +5915,43 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="R46" t="n">
-        <v>0.04730000000000001</v>
+        <v>0.0473</v>
       </c>
       <c r="S46" t="n">
-        <v>0.04730000000000001</v>
+        <v>0.0473</v>
       </c>
       <c r="T46" t="n">
-        <v>0.04730000000000001</v>
+        <v>0.0473</v>
       </c>
       <c r="U46" t="n">
-        <v>0.04730000000000001</v>
+        <v>0.0473</v>
       </c>
       <c r="V46" t="n">
-        <v>0.04730000000000001</v>
+        <v>0.0473</v>
       </c>
       <c r="W46" t="n">
-        <v>0.04730000000000001</v>
+        <v>0.0473</v>
       </c>
       <c r="X46" t="n">
-        <v>0.04730000000000001</v>
+        <v>0.0473</v>
       </c>
       <c r="Y46" t="n">
-        <v>0.04730000000000001</v>
+        <v>0.0473</v>
       </c>
       <c r="Z46" t="n">
-        <v>0.04730000000000001</v>
+        <v>0.0473</v>
       </c>
       <c r="AA46" t="n">
-        <v>0.04730000000000001</v>
+        <v>0.0473</v>
       </c>
       <c r="AB46" t="n">
-        <v>0.04730000000000001</v>
+        <v>0.0473</v>
       </c>
       <c r="AC46" t="n">
-        <v>0.04730000000000001</v>
+        <v>0.0473</v>
       </c>
       <c r="AD46" t="n">
         <v>0.1769230769230769</v>
@@ -6124,25 +6124,25 @@
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="n">
-        <v>0.839671991015207</v>
+        <v>2.149694693288204</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>0.3862608333712286</v>
+        <v>0.3698348586337275</v>
       </c>
       <c r="I48" t="n">
-        <v>0.05808330630630155</v>
+        <v>0.07181435772930708</v>
       </c>
       <c r="J48" t="n">
-        <v>2.789528200678129</v>
+        <v>1.668368956047404</v>
       </c>
       <c r="K48" t="n">
-        <v>55.82011708957287</v>
+        <v>37.76399442323535</v>
       </c>
       <c r="L48" t="n">
-        <v>0.3577729371573858</v>
+        <v>0.2276008900279758</v>
       </c>
       <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
@@ -6153,79 +6153,79 @@
         <v>1</v>
       </c>
       <c r="Q48" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="R48" t="n">
-        <v>0.05808330630630155</v>
+        <v>0.07181435772930708</v>
       </c>
       <c r="S48" t="n">
-        <v>0.05808330630630155</v>
+        <v>0.07181435772930708</v>
       </c>
       <c r="T48" t="n">
-        <v>0.05808330630630155</v>
+        <v>0.07181435772930708</v>
       </c>
       <c r="U48" t="n">
-        <v>0.05808330630630155</v>
+        <v>0.07181435772930708</v>
       </c>
       <c r="V48" t="n">
-        <v>0.05808330630630155</v>
+        <v>0.07181435772930708</v>
       </c>
       <c r="W48" t="n">
-        <v>0.05808330630630155</v>
+        <v>0.07181435772930708</v>
       </c>
       <c r="X48" t="n">
-        <v>0.05808330630630155</v>
+        <v>0.07181435772930708</v>
       </c>
       <c r="Y48" t="n">
-        <v>0.05808330630630155</v>
+        <v>0.07181435772930708</v>
       </c>
       <c r="Z48" t="n">
-        <v>0.05808330630630155</v>
+        <v>0.07181435772930708</v>
       </c>
       <c r="AA48" t="n">
-        <v>0.05808330630630155</v>
+        <v>0.07181435772930708</v>
       </c>
       <c r="AB48" t="n">
-        <v>0.05808330630630155</v>
+        <v>0.07181435772930708</v>
       </c>
       <c r="AC48" t="n">
-        <v>0.05808330630630155</v>
+        <v>0.07181435772930708</v>
       </c>
       <c r="AD48" t="n">
-        <v>0.1097303694703608</v>
+        <v>0.04722592715241693</v>
       </c>
       <c r="AE48" t="n">
-        <v>0.1097303694703608</v>
+        <v>0.04722592715241693</v>
       </c>
       <c r="AF48" t="n">
-        <v>0.1097303694703608</v>
+        <v>0.04722592715241693</v>
       </c>
       <c r="AG48" t="n">
-        <v>0.1958972122730448</v>
+        <v>0.1593927632868605</v>
       </c>
       <c r="AH48" t="n">
-        <v>0.1958972122730448</v>
+        <v>0.1593927632868605</v>
       </c>
       <c r="AI48" t="n">
-        <v>0.1958972122730448</v>
+        <v>0.1593927632868605</v>
       </c>
       <c r="AJ48" t="n">
-        <v>0.1958972122730448</v>
+        <v>0.1593927632868605</v>
       </c>
       <c r="AK48" t="n">
-        <v>0.1958972122730448</v>
+        <v>0.1593927632868605</v>
       </c>
       <c r="AL48" t="n">
-        <v>0.1958972122730448</v>
+        <v>0.1593927632868605</v>
       </c>
       <c r="AM48" t="n">
-        <v>0.1097303694703608</v>
+        <v>0.04722592715241693</v>
       </c>
       <c r="AN48" t="n">
-        <v>0.1097303694703608</v>
+        <v>0.04722592715241693</v>
       </c>
       <c r="AO48" t="n">
-        <v>0.1097303694703608</v>
+        <v>0.04722592715241693</v>
       </c>
     </row>
     <row r="49">
@@ -6362,16 +6362,16 @@
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="n">
-        <v>0.5545283018867925</v>
+        <v>0.8564150943396227</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>0.3725590879599593</v>
+        <v>0.3750102554540369</v>
       </c>
       <c r="I50" t="n">
-        <v>0.03900000000000001</v>
+        <v>0.03899999999999999</v>
       </c>
       <c r="J50" t="n">
         <v>2.78</v>
@@ -6391,43 +6391,43 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R50" t="n">
-        <v>0.03900000000000001</v>
+        <v>0.03899999999999999</v>
       </c>
       <c r="S50" t="n">
-        <v>0.03900000000000001</v>
+        <v>0.03899999999999999</v>
       </c>
       <c r="T50" t="n">
-        <v>0.03900000000000001</v>
+        <v>0.03899999999999999</v>
       </c>
       <c r="U50" t="n">
-        <v>0.03900000000000001</v>
+        <v>0.03899999999999999</v>
       </c>
       <c r="V50" t="n">
-        <v>0.03900000000000001</v>
+        <v>0.03899999999999999</v>
       </c>
       <c r="W50" t="n">
-        <v>0.03900000000000001</v>
+        <v>0.03899999999999999</v>
       </c>
       <c r="X50" t="n">
-        <v>0.03900000000000001</v>
+        <v>0.03899999999999999</v>
       </c>
       <c r="Y50" t="n">
-        <v>0.03900000000000001</v>
+        <v>0.03899999999999999</v>
       </c>
       <c r="Z50" t="n">
-        <v>0.03900000000000001</v>
+        <v>0.03899999999999999</v>
       </c>
       <c r="AA50" t="n">
-        <v>0.03900000000000001</v>
+        <v>0.03899999999999999</v>
       </c>
       <c r="AB50" t="n">
-        <v>0.03900000000000001</v>
+        <v>0.03899999999999999</v>
       </c>
       <c r="AC50" t="n">
-        <v>0.03900000000000001</v>
+        <v>0.03899999999999999</v>
       </c>
       <c r="AD50" t="n">
         <v>0.08307692307692306</v>
@@ -6719,25 +6719,25 @@
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="n">
-        <v>3.758370904718967</v>
+        <v>3.88458070333634</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>0.3880509115842076</v>
+        <v>0.3876728299095888</v>
       </c>
       <c r="I53" t="n">
-        <v>0.04729999999999999</v>
+        <v>0.04730000000000002</v>
       </c>
       <c r="J53" t="n">
-        <v>3.67</v>
+        <v>3.670000000000001</v>
       </c>
       <c r="K53" t="n">
-        <v>69.99999999999999</v>
+        <v>70.00000000000001</v>
       </c>
       <c r="L53" t="n">
-        <v>0.4599999999999999</v>
+        <v>0.46</v>
       </c>
       <c r="M53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
@@ -6748,79 +6748,79 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="R53" t="n">
-        <v>0.04729999999999999</v>
+        <v>0.04730000000000002</v>
       </c>
       <c r="S53" t="n">
-        <v>0.04729999999999999</v>
+        <v>0.04730000000000002</v>
       </c>
       <c r="T53" t="n">
-        <v>0.04729999999999999</v>
+        <v>0.04730000000000002</v>
       </c>
       <c r="U53" t="n">
-        <v>0.04729999999999999</v>
+        <v>0.04730000000000002</v>
       </c>
       <c r="V53" t="n">
-        <v>0.04729999999999999</v>
+        <v>0.04730000000000002</v>
       </c>
       <c r="W53" t="n">
-        <v>0.04729999999999999</v>
+        <v>0.04730000000000002</v>
       </c>
       <c r="X53" t="n">
-        <v>0.04729999999999999</v>
+        <v>0.04730000000000002</v>
       </c>
       <c r="Y53" t="n">
-        <v>0.04729999999999999</v>
+        <v>0.04730000000000002</v>
       </c>
       <c r="Z53" t="n">
-        <v>0.04729999999999999</v>
+        <v>0.04730000000000002</v>
       </c>
       <c r="AA53" t="n">
-        <v>0.04729999999999999</v>
+        <v>0.04730000000000002</v>
       </c>
       <c r="AB53" t="n">
-        <v>0.04729999999999999</v>
+        <v>0.04730000000000002</v>
       </c>
       <c r="AC53" t="n">
-        <v>0.04729999999999999</v>
+        <v>0.04730000000000002</v>
       </c>
       <c r="AD53" t="n">
-        <v>0.1769230769230768</v>
+        <v>0.1769230769230769</v>
       </c>
       <c r="AE53" t="n">
-        <v>0.1769230769230768</v>
+        <v>0.1769230769230769</v>
       </c>
       <c r="AF53" t="n">
-        <v>0.1769230769230768</v>
+        <v>0.1769230769230769</v>
       </c>
       <c r="AG53" t="n">
-        <v>0.2065573770491803</v>
+        <v>0.2065573770491804</v>
       </c>
       <c r="AH53" t="n">
-        <v>0.2065573770491803</v>
+        <v>0.2065573770491804</v>
       </c>
       <c r="AI53" t="n">
-        <v>0.2065573770491803</v>
+        <v>0.2065573770491804</v>
       </c>
       <c r="AJ53" t="n">
-        <v>0.2065573770491803</v>
+        <v>0.2065573770491804</v>
       </c>
       <c r="AK53" t="n">
-        <v>0.2065573770491803</v>
+        <v>0.2065573770491804</v>
       </c>
       <c r="AL53" t="n">
-        <v>0.2065573770491803</v>
+        <v>0.2065573770491804</v>
       </c>
       <c r="AM53" t="n">
-        <v>0.1769230769230768</v>
+        <v>0.1769230769230769</v>
       </c>
       <c r="AN53" t="n">
-        <v>0.1769230769230768</v>
+        <v>0.1769230769230769</v>
       </c>
       <c r="AO53" t="n">
-        <v>0.1769230769230768</v>
+        <v>0.1769230769230769</v>
       </c>
     </row>
     <row r="54">
@@ -6838,25 +6838,25 @@
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="n">
-        <v>1.411875</v>
+        <v>1.553625</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>0.4140347501882102</v>
+        <v>0.4143429034662488</v>
       </c>
       <c r="I54" t="n">
         <v>0.04730000000000001</v>
       </c>
       <c r="J54" t="n">
-        <v>3.669999999999999</v>
+        <v>3.67</v>
       </c>
       <c r="K54" t="n">
         <v>70</v>
       </c>
       <c r="L54" t="n">
-        <v>0.46</v>
+        <v>0.4600000000000001</v>
       </c>
       <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr"/>
@@ -6867,7 +6867,7 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="R54" t="n">
         <v>0.04730000000000001</v>
@@ -6906,13 +6906,13 @@
         <v>0.04730000000000001</v>
       </c>
       <c r="AD54" t="n">
-        <v>0.1769230769230769</v>
+        <v>0.176923076923077</v>
       </c>
       <c r="AE54" t="n">
-        <v>0.1769230769230769</v>
+        <v>0.176923076923077</v>
       </c>
       <c r="AF54" t="n">
-        <v>0.1769230769230769</v>
+        <v>0.176923076923077</v>
       </c>
       <c r="AG54" t="n">
         <v>0.2065573770491803</v>
@@ -6933,13 +6933,13 @@
         <v>0.2065573770491803</v>
       </c>
       <c r="AM54" t="n">
-        <v>0.1769230769230769</v>
+        <v>0.176923076923077</v>
       </c>
       <c r="AN54" t="n">
-        <v>0.1769230769230769</v>
+        <v>0.176923076923077</v>
       </c>
       <c r="AO54" t="n">
-        <v>0.1769230769230769</v>
+        <v>0.176923076923077</v>
       </c>
     </row>
     <row r="55">
@@ -6957,25 +6957,25 @@
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="n">
-        <v>0.8293868921775899</v>
+        <v>0.8436046511627907</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>0.320233186388691</v>
+        <v>0.3202292296143972</v>
       </c>
       <c r="I55" t="n">
-        <v>0.0473</v>
+        <v>0.04729999999999999</v>
       </c>
       <c r="J55" t="n">
         <v>3.67</v>
       </c>
       <c r="K55" t="n">
-        <v>70.00000000000001</v>
+        <v>70</v>
       </c>
       <c r="L55" t="n">
-        <v>0.4600000000000001</v>
+        <v>0.46</v>
       </c>
       <c r="M55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
@@ -6986,52 +6986,52 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="R55" t="n">
-        <v>0.0473</v>
+        <v>0.04729999999999999</v>
       </c>
       <c r="S55" t="n">
-        <v>0.0473</v>
+        <v>0.04729999999999999</v>
       </c>
       <c r="T55" t="n">
-        <v>0.0473</v>
+        <v>0.04729999999999999</v>
       </c>
       <c r="U55" t="n">
-        <v>0.0473</v>
+        <v>0.04729999999999999</v>
       </c>
       <c r="V55" t="n">
-        <v>0.0473</v>
+        <v>0.04729999999999999</v>
       </c>
       <c r="W55" t="n">
-        <v>0.0473</v>
+        <v>0.04729999999999999</v>
       </c>
       <c r="X55" t="n">
-        <v>0.0473</v>
+        <v>0.04729999999999999</v>
       </c>
       <c r="Y55" t="n">
-        <v>0.0473</v>
+        <v>0.04729999999999999</v>
       </c>
       <c r="Z55" t="n">
-        <v>0.0473</v>
+        <v>0.04729999999999999</v>
       </c>
       <c r="AA55" t="n">
-        <v>0.0473</v>
+        <v>0.04729999999999999</v>
       </c>
       <c r="AB55" t="n">
-        <v>0.0473</v>
+        <v>0.04729999999999999</v>
       </c>
       <c r="AC55" t="n">
-        <v>0.0473</v>
+        <v>0.04729999999999999</v>
       </c>
       <c r="AD55" t="n">
-        <v>0.176923076923077</v>
+        <v>0.1769230769230769</v>
       </c>
       <c r="AE55" t="n">
-        <v>0.176923076923077</v>
+        <v>0.1769230769230769</v>
       </c>
       <c r="AF55" t="n">
-        <v>0.176923076923077</v>
+        <v>0.1769230769230769</v>
       </c>
       <c r="AG55" t="n">
         <v>0.2065573770491803</v>
@@ -7052,13 +7052,13 @@
         <v>0.2065573770491803</v>
       </c>
       <c r="AM55" t="n">
-        <v>0.176923076923077</v>
+        <v>0.1769230769230769</v>
       </c>
       <c r="AN55" t="n">
-        <v>0.176923076923077</v>
+        <v>0.1769230769230769</v>
       </c>
       <c r="AO55" t="n">
-        <v>0.176923076923077</v>
+        <v>0.1769230769230769</v>
       </c>
     </row>
     <row r="56">
@@ -7558,10 +7558,10 @@
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>0.324331100082713</v>
+        <v>0.3191022967553773</v>
       </c>
       <c r="I60" t="n">
-        <v>0.08265134776844894</v>
+        <v>0.08233720703759008</v>
       </c>
       <c r="J60" t="n">
         <v>1</v>
@@ -7581,43 +7581,43 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="R60" t="n">
-        <v>0.08265134776844894</v>
+        <v>0.08233720703759008</v>
       </c>
       <c r="S60" t="n">
-        <v>0.08265134776844894</v>
+        <v>0.08233720703759008</v>
       </c>
       <c r="T60" t="n">
-        <v>0.08265134776844894</v>
+        <v>0.08233720703759008</v>
       </c>
       <c r="U60" t="n">
-        <v>0.08265134776844894</v>
+        <v>0.08233720703759008</v>
       </c>
       <c r="V60" t="n">
-        <v>0.08265134776844894</v>
+        <v>0.08233720703759008</v>
       </c>
       <c r="W60" t="n">
-        <v>0.08265134776844894</v>
+        <v>0.08233720703759008</v>
       </c>
       <c r="X60" t="n">
-        <v>0.08265134776844894</v>
+        <v>0.08233720703759008</v>
       </c>
       <c r="Y60" t="n">
-        <v>0.08265134776844894</v>
+        <v>0.08233720703759008</v>
       </c>
       <c r="Z60" t="n">
-        <v>0.08265134776844894</v>
+        <v>0.08233720703759008</v>
       </c>
       <c r="AA60" t="n">
-        <v>0.08265134776844894</v>
+        <v>0.08233720703759008</v>
       </c>
       <c r="AB60" t="n">
-        <v>0.08265134776844894</v>
+        <v>0.08233720703759008</v>
       </c>
       <c r="AC60" t="n">
-        <v>0.08265134776844894</v>
+        <v>0.08233720703759008</v>
       </c>
       <c r="AD60" t="n">
         <v>0.01071428571428571</v>
@@ -7629,22 +7629,22 @@
         <v>0.01071428571428571</v>
       </c>
       <c r="AG60" t="n">
-        <v>0.06038251366120219</v>
+        <v>0.06038251366120218</v>
       </c>
       <c r="AH60" t="n">
-        <v>0.06038251366120219</v>
+        <v>0.06038251366120218</v>
       </c>
       <c r="AI60" t="n">
-        <v>0.06038251366120219</v>
+        <v>0.06038251366120218</v>
       </c>
       <c r="AJ60" t="n">
-        <v>0.06038251366120219</v>
+        <v>0.06038251366120218</v>
       </c>
       <c r="AK60" t="n">
-        <v>0.06038251366120219</v>
+        <v>0.06038251366120218</v>
       </c>
       <c r="AL60" t="n">
-        <v>0.06038251366120219</v>
+        <v>0.06038251366120218</v>
       </c>
       <c r="AM60" t="n">
         <v>0.01071428571428571</v>
@@ -8742,7 +8742,7 @@
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr"/>
       <c r="F70" t="n">
-        <v>2.067475409836065</v>
+        <v>2.067475409836066</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -8751,7 +8751,7 @@
         <v>0.2394963447885569</v>
       </c>
       <c r="I70" t="n">
-        <v>0.1092900387639263</v>
+        <v>0.1092900387639264</v>
       </c>
       <c r="J70" t="n">
         <v>1</v>
@@ -8774,40 +8774,40 @@
         <v>22</v>
       </c>
       <c r="R70" t="n">
-        <v>0.1092900387639263</v>
+        <v>0.1092900387639264</v>
       </c>
       <c r="S70" t="n">
-        <v>0.1092900387639263</v>
+        <v>0.1092900387639264</v>
       </c>
       <c r="T70" t="n">
-        <v>0.1092900387639263</v>
+        <v>0.1092900387639264</v>
       </c>
       <c r="U70" t="n">
-        <v>0.1092900387639263</v>
+        <v>0.1092900387639264</v>
       </c>
       <c r="V70" t="n">
-        <v>0.1092900387639263</v>
+        <v>0.1092900387639264</v>
       </c>
       <c r="W70" t="n">
-        <v>0.1092900387639263</v>
+        <v>0.1092900387639264</v>
       </c>
       <c r="X70" t="n">
-        <v>0.1092900387639263</v>
+        <v>0.1092900387639264</v>
       </c>
       <c r="Y70" t="n">
-        <v>0.1092900387639263</v>
+        <v>0.1092900387639264</v>
       </c>
       <c r="Z70" t="n">
-        <v>0.1092900387639263</v>
+        <v>0.1092900387639264</v>
       </c>
       <c r="AA70" t="n">
-        <v>0.1092900387639263</v>
+        <v>0.1092900387639264</v>
       </c>
       <c r="AB70" t="n">
-        <v>0.1092900387639263</v>
+        <v>0.1092900387639264</v>
       </c>
       <c r="AC70" t="n">
-        <v>0.1092900387639263</v>
+        <v>0.1092900387639264</v>
       </c>
       <c r="AD70" t="n">
         <v>0.02225274725274726</v>
@@ -8861,13 +8861,13 @@
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr"/>
       <c r="F71" t="n">
-        <v>1.398</v>
+        <v>2.214</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>0.3255721030042918</v>
+        <v>0.3565417344173442</v>
       </c>
       <c r="I71" t="n">
         <v>0.1156164383561643</v>
@@ -8879,7 +8879,7 @@
         <v>13</v>
       </c>
       <c r="L71" t="n">
-        <v>0.15</v>
+        <v>0.1499999999999999</v>
       </c>
       <c r="M71" t="inlineStr"/>
       <c r="N71" t="inlineStr"/>
@@ -8890,7 +8890,7 @@
         <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R71" t="n">
         <v>0.1156164383561643</v>
@@ -8989,7 +8989,7 @@
         <v>0.407174850719868</v>
       </c>
       <c r="I72" t="n">
-        <v>0.01948101868665202</v>
+        <v>0.01948101868665203</v>
       </c>
       <c r="J72" t="n">
         <v>1</v>
@@ -9012,49 +9012,49 @@
         <v>6</v>
       </c>
       <c r="R72" t="n">
-        <v>0.01948101868665202</v>
+        <v>0.01948101868665203</v>
       </c>
       <c r="S72" t="n">
-        <v>0.01948101868665202</v>
+        <v>0.01948101868665203</v>
       </c>
       <c r="T72" t="n">
-        <v>0.01948101868665202</v>
+        <v>0.01948101868665203</v>
       </c>
       <c r="U72" t="n">
-        <v>0.01948101868665202</v>
+        <v>0.01948101868665203</v>
       </c>
       <c r="V72" t="n">
-        <v>0.01948101868665202</v>
+        <v>0.01948101868665203</v>
       </c>
       <c r="W72" t="n">
-        <v>0.01948101868665202</v>
+        <v>0.01948101868665203</v>
       </c>
       <c r="X72" t="n">
-        <v>0.01948101868665202</v>
+        <v>0.01948101868665203</v>
       </c>
       <c r="Y72" t="n">
-        <v>0.01948101868665202</v>
+        <v>0.01948101868665203</v>
       </c>
       <c r="Z72" t="n">
-        <v>0.01948101868665202</v>
+        <v>0.01948101868665203</v>
       </c>
       <c r="AA72" t="n">
-        <v>0.01948101868665202</v>
+        <v>0.01948101868665203</v>
       </c>
       <c r="AB72" t="n">
-        <v>0.01948101868665202</v>
+        <v>0.01948101868665203</v>
       </c>
       <c r="AC72" t="n">
-        <v>0.01948101868665202</v>
+        <v>0.01948101868665203</v>
       </c>
       <c r="AD72" t="n">
-        <v>0.01071428571428571</v>
+        <v>0.01071428571428572</v>
       </c>
       <c r="AE72" t="n">
-        <v>0.01071428571428571</v>
+        <v>0.01071428571428572</v>
       </c>
       <c r="AF72" t="n">
-        <v>0.01071428571428571</v>
+        <v>0.01071428571428572</v>
       </c>
       <c r="AG72" t="n">
         <v>0.06038251366120219</v>
@@ -9075,13 +9075,13 @@
         <v>0.06038251366120219</v>
       </c>
       <c r="AM72" t="n">
-        <v>0.01071428571428571</v>
+        <v>0.01071428571428572</v>
       </c>
       <c r="AN72" t="n">
-        <v>0.01071428571428571</v>
+        <v>0.01071428571428572</v>
       </c>
       <c r="AO72" t="n">
-        <v>0.01071428571428571</v>
+        <v>0.01071428571428572</v>
       </c>
     </row>
     <row r="73">
@@ -9575,7 +9575,7 @@
       <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr"/>
       <c r="F77" t="n">
-        <v>22.80864672001289</v>
+        <v>23.53484398915174</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -9584,7 +9584,7 @@
         <v>0.4799999999999999</v>
       </c>
       <c r="I77" t="n">
-        <v>0.08</v>
+        <v>0.08000000000000002</v>
       </c>
       <c r="J77" t="n">
         <v>1</v>
@@ -9604,79 +9604,79 @@
         <v>1</v>
       </c>
       <c r="Q77" t="n">
-        <v>307</v>
+        <v>347</v>
       </c>
       <c r="R77" t="n">
-        <v>0.08</v>
+        <v>0.08000000000000002</v>
       </c>
       <c r="S77" t="n">
-        <v>0.08</v>
+        <v>0.08000000000000002</v>
       </c>
       <c r="T77" t="n">
-        <v>0.08</v>
+        <v>0.08000000000000002</v>
       </c>
       <c r="U77" t="n">
-        <v>0.08</v>
+        <v>0.08000000000000002</v>
       </c>
       <c r="V77" t="n">
-        <v>0.08</v>
+        <v>0.08000000000000002</v>
       </c>
       <c r="W77" t="n">
-        <v>0.08</v>
+        <v>0.08000000000000002</v>
       </c>
       <c r="X77" t="n">
-        <v>0.08</v>
+        <v>0.08000000000000002</v>
       </c>
       <c r="Y77" t="n">
-        <v>0.08</v>
+        <v>0.08000000000000002</v>
       </c>
       <c r="Z77" t="n">
-        <v>0.08</v>
+        <v>0.08000000000000002</v>
       </c>
       <c r="AA77" t="n">
-        <v>0.08</v>
+        <v>0.08000000000000002</v>
       </c>
       <c r="AB77" t="n">
-        <v>0.08</v>
+        <v>0.08000000000000002</v>
       </c>
       <c r="AC77" t="n">
-        <v>0.08</v>
+        <v>0.08000000000000002</v>
       </c>
       <c r="AD77" t="n">
-        <v>0.02225274725274725</v>
+        <v>0.02225274725274726</v>
       </c>
       <c r="AE77" t="n">
-        <v>0.02225274725274725</v>
+        <v>0.02225274725274726</v>
       </c>
       <c r="AF77" t="n">
-        <v>0.02225274725274725</v>
+        <v>0.02225274725274726</v>
       </c>
       <c r="AG77" t="n">
-        <v>0.1254098360655737</v>
+        <v>0.1254098360655738</v>
       </c>
       <c r="AH77" t="n">
-        <v>0.1254098360655737</v>
+        <v>0.1254098360655738</v>
       </c>
       <c r="AI77" t="n">
-        <v>0.1254098360655737</v>
+        <v>0.1254098360655738</v>
       </c>
       <c r="AJ77" t="n">
-        <v>0.1254098360655737</v>
+        <v>0.1254098360655738</v>
       </c>
       <c r="AK77" t="n">
-        <v>0.1254098360655737</v>
+        <v>0.1254098360655738</v>
       </c>
       <c r="AL77" t="n">
-        <v>0.1254098360655737</v>
+        <v>0.1254098360655738</v>
       </c>
       <c r="AM77" t="n">
-        <v>0.02225274725274725</v>
+        <v>0.02225274725274726</v>
       </c>
       <c r="AN77" t="n">
-        <v>0.02225274725274725</v>
+        <v>0.02225274725274726</v>
       </c>
       <c r="AO77" t="n">
-        <v>0.02225274725274725</v>
+        <v>0.02225274725274726</v>
       </c>
     </row>
     <row r="78">
@@ -9932,7 +9932,7 @@
       <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr"/>
       <c r="F80" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -9947,10 +9947,10 @@
         <v>2</v>
       </c>
       <c r="K80" t="n">
-        <v>135</v>
+        <v>97.5</v>
       </c>
       <c r="L80" t="n">
-        <v>0.075</v>
+        <v>0.0375</v>
       </c>
       <c r="M80" t="inlineStr"/>
       <c r="N80" t="inlineStr"/>
@@ -9961,7 +9961,7 @@
         <v>0</v>
       </c>
       <c r="Q80" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R80" t="n">
         <v>0.04</v>
@@ -10000,40 +10000,40 @@
         <v>0.04</v>
       </c>
       <c r="AD80" t="n">
-        <v>0.05563186813186814</v>
+        <v>0.02008928571428571</v>
       </c>
       <c r="AE80" t="n">
-        <v>0.05563186813186814</v>
+        <v>0.02008928571428571</v>
       </c>
       <c r="AF80" t="n">
-        <v>0.05563186813186814</v>
+        <v>0.02008928571428571</v>
       </c>
       <c r="AG80" t="n">
-        <v>0.6823770491803279</v>
+        <v>0.5128073770491803</v>
       </c>
       <c r="AH80" t="n">
-        <v>0.6823770491803279</v>
+        <v>0.5128073770491803</v>
       </c>
       <c r="AI80" t="n">
-        <v>0.6823770491803279</v>
+        <v>0.5128073770491803</v>
       </c>
       <c r="AJ80" t="n">
-        <v>0.6823770491803279</v>
+        <v>0.5128073770491803</v>
       </c>
       <c r="AK80" t="n">
-        <v>0.6823770491803279</v>
+        <v>0.5128073770491803</v>
       </c>
       <c r="AL80" t="n">
-        <v>0.6823770491803279</v>
+        <v>0.5128073770491803</v>
       </c>
       <c r="AM80" t="n">
-        <v>0.05563186813186814</v>
+        <v>0.02008928571428571</v>
       </c>
       <c r="AN80" t="n">
-        <v>0.05563186813186814</v>
+        <v>0.02008928571428571</v>
       </c>
       <c r="AO80" t="n">
-        <v>0.05563186813186814</v>
+        <v>0.02008928571428571</v>
       </c>
     </row>
     <row r="81">
@@ -11122,7 +11122,7 @@
       <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr"/>
       <c r="F90" t="n">
-        <v>0.6186868686868687</v>
+        <v>1.237373737373737</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -11151,7 +11151,7 @@
         <v>0</v>
       </c>
       <c r="Q90" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R90" t="n">
         <v>0.05</v>
@@ -11241,7 +11241,7 @@
       <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr"/>
       <c r="F91" t="n">
-        <v>3.898550724637681</v>
+        <v>4.347826086956522</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -11270,7 +11270,7 @@
         <v>0</v>
       </c>
       <c r="Q91" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="R91" t="n">
         <v>0.05</v>
@@ -11369,7 +11369,7 @@
         <v>0.36</v>
       </c>
       <c r="I92" t="n">
-        <v>0.07999999999999999</v>
+        <v>0.08</v>
       </c>
       <c r="J92" t="n">
         <v>1</v>
@@ -11389,43 +11389,43 @@
         <v>1</v>
       </c>
       <c r="Q92" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="R92" t="n">
-        <v>0.07999999999999999</v>
+        <v>0.08</v>
       </c>
       <c r="S92" t="n">
-        <v>0.07999999999999999</v>
+        <v>0.08</v>
       </c>
       <c r="T92" t="n">
-        <v>0.07999999999999999</v>
+        <v>0.08</v>
       </c>
       <c r="U92" t="n">
-        <v>0.07999999999999999</v>
+        <v>0.08</v>
       </c>
       <c r="V92" t="n">
-        <v>0.07999999999999999</v>
+        <v>0.08</v>
       </c>
       <c r="W92" t="n">
-        <v>0.07999999999999999</v>
+        <v>0.08</v>
       </c>
       <c r="X92" t="n">
-        <v>0.07999999999999999</v>
+        <v>0.08</v>
       </c>
       <c r="Y92" t="n">
-        <v>0.07999999999999999</v>
+        <v>0.08</v>
       </c>
       <c r="Z92" t="n">
-        <v>0.07999999999999999</v>
+        <v>0.08</v>
       </c>
       <c r="AA92" t="n">
-        <v>0.07999999999999999</v>
+        <v>0.08</v>
       </c>
       <c r="AB92" t="n">
-        <v>0.07999999999999999</v>
+        <v>0.08</v>
       </c>
       <c r="AC92" t="n">
-        <v>0.07999999999999999</v>
+        <v>0.08</v>
       </c>
       <c r="AD92" t="n">
         <v>0.02225274725274725</v>
@@ -11598,7 +11598,7 @@
       <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr"/>
       <c r="F94" t="n">
-        <v>24.83872727272727</v>
+        <v>25.20472727272728</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -11627,7 +11627,7 @@
         <v>1</v>
       </c>
       <c r="Q94" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="R94" t="n">
         <v>0</v>
@@ -11717,7 +11717,7 @@
       <c r="D95" t="inlineStr"/>
       <c r="E95" t="inlineStr"/>
       <c r="F95" t="n">
-        <v>0.6326530612244898</v>
+        <v>1.13265306122449</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -11746,7 +11746,7 @@
         <v>0</v>
       </c>
       <c r="Q95" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R95" t="n">
         <v>0.05</v>
@@ -12431,7 +12431,7 @@
       <c r="D101" t="inlineStr"/>
       <c r="E101" t="inlineStr"/>
       <c r="F101" t="n">
-        <v>0.2089951513124896</v>
+        <v>0.6269854539374686</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -12440,13 +12440,13 @@
         <v>0.35</v>
       </c>
       <c r="I101" t="n">
-        <v>0.08</v>
+        <v>0.08000000000000002</v>
       </c>
       <c r="J101" t="n">
         <v>1</v>
       </c>
       <c r="K101" t="n">
-        <v>7</v>
+        <v>7.000000000000001</v>
       </c>
       <c r="L101" t="n">
         <v>0.15</v>
@@ -12460,43 +12460,43 @@
         <v>0</v>
       </c>
       <c r="Q101" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R101" t="n">
-        <v>0.08</v>
+        <v>0.08000000000000002</v>
       </c>
       <c r="S101" t="n">
-        <v>0.08</v>
+        <v>0.08000000000000002</v>
       </c>
       <c r="T101" t="n">
-        <v>0.08</v>
+        <v>0.08000000000000002</v>
       </c>
       <c r="U101" t="n">
-        <v>0.08</v>
+        <v>0.08000000000000002</v>
       </c>
       <c r="V101" t="n">
-        <v>0.08</v>
+        <v>0.08000000000000002</v>
       </c>
       <c r="W101" t="n">
-        <v>0.08</v>
+        <v>0.08000000000000002</v>
       </c>
       <c r="X101" t="n">
-        <v>0.08</v>
+        <v>0.08000000000000002</v>
       </c>
       <c r="Y101" t="n">
-        <v>0.08</v>
+        <v>0.08000000000000002</v>
       </c>
       <c r="Z101" t="n">
-        <v>0.08</v>
+        <v>0.08000000000000002</v>
       </c>
       <c r="AA101" t="n">
-        <v>0.08</v>
+        <v>0.08000000000000002</v>
       </c>
       <c r="AB101" t="n">
-        <v>0.08</v>
+        <v>0.08000000000000002</v>
       </c>
       <c r="AC101" t="n">
-        <v>0.08</v>
+        <v>0.08000000000000002</v>
       </c>
       <c r="AD101" t="n">
         <v>0.00576923076923077</v>
@@ -12550,13 +12550,13 @@
       <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr"/>
       <c r="F102" t="n">
-        <v>0.7542857142857142</v>
+        <v>1.154285714285714</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
       </c>
       <c r="H102" t="n">
-        <v>0.5600000000000002</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I102" t="n">
         <v>0.05</v>
@@ -12579,7 +12579,7 @@
         <v>0</v>
       </c>
       <c r="Q102" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R102" t="n">
         <v>0.05</v>
@@ -13502,7 +13502,7 @@
       <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr"/>
       <c r="F110" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
@@ -13531,7 +13531,7 @@
         <v>0</v>
       </c>
       <c r="Q110" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R110" t="n">
         <v>0.075</v>
@@ -13740,13 +13740,13 @@
       <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr"/>
       <c r="F112" t="n">
-        <v>1.35593220338983</v>
+        <v>1.627118644067797</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
       </c>
       <c r="H112" t="n">
-        <v>0.3377791170709658</v>
+        <v>0.3337947159223755</v>
       </c>
       <c r="I112" t="n">
         <v>0.05</v>
@@ -13755,7 +13755,7 @@
         <v>7</v>
       </c>
       <c r="K112" t="n">
-        <v>38.40289287328612</v>
+        <v>29.79658639233107</v>
       </c>
       <c r="L112" t="n">
         <v>0.15</v>
@@ -13769,7 +13769,7 @@
         <v>1</v>
       </c>
       <c r="Q112" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="R112" t="n">
         <v>0.05</v>
@@ -13808,40 +13808,40 @@
         <v>0.05</v>
       </c>
       <c r="AD112" t="n">
-        <v>0.03165073588457647</v>
+        <v>0.02455762614752561</v>
       </c>
       <c r="AE112" t="n">
-        <v>0.03165073588457647</v>
+        <v>0.02455762614752561</v>
       </c>
       <c r="AF112" t="n">
-        <v>0.03165073588457647</v>
+        <v>0.02455762614752561</v>
       </c>
       <c r="AG112" t="n">
-        <v>0.1783740925808372</v>
+        <v>0.1383994449917017</v>
       </c>
       <c r="AH112" t="n">
-        <v>0.1783740925808372</v>
+        <v>0.1383994449917017</v>
       </c>
       <c r="AI112" t="n">
-        <v>0.1783740925808372</v>
+        <v>0.1383994449917017</v>
       </c>
       <c r="AJ112" t="n">
-        <v>0.1783740925808372</v>
+        <v>0.1383994449917017</v>
       </c>
       <c r="AK112" t="n">
-        <v>0.1783740925808372</v>
+        <v>0.1383994449917017</v>
       </c>
       <c r="AL112" t="n">
-        <v>0.1783740925808372</v>
+        <v>0.1383994449917017</v>
       </c>
       <c r="AM112" t="n">
-        <v>0.03165073588457647</v>
+        <v>0.02455762614752561</v>
       </c>
       <c r="AN112" t="n">
-        <v>0.03165073588457647</v>
+        <v>0.02455762614752561</v>
       </c>
       <c r="AO112" t="n">
-        <v>0.03165073588457647</v>
+        <v>0.02455762614752561</v>
       </c>
     </row>
     <row r="113">
@@ -14811,22 +14811,22 @@
       <c r="D121" t="inlineStr"/>
       <c r="E121" t="inlineStr"/>
       <c r="F121" t="n">
-        <v>0.9355999999999999</v>
+        <v>2.839999999999999</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
       </c>
       <c r="H121" t="n">
-        <v>0.4463847399676085</v>
+        <v>0.4692988084326307</v>
       </c>
       <c r="I121" t="n">
-        <v>0.03995627136944394</v>
+        <v>0.04719786892758936</v>
       </c>
       <c r="J121" t="n">
         <v>1</v>
       </c>
       <c r="K121" t="n">
-        <v>17.40093575670326</v>
+        <v>17.5627864344638</v>
       </c>
       <c r="L121" t="n">
         <v>0.15</v>
@@ -14840,79 +14840,79 @@
         <v>0</v>
       </c>
       <c r="Q121" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="R121" t="n">
-        <v>0.03995627136944394</v>
+        <v>0.04719786892758936</v>
       </c>
       <c r="S121" t="n">
-        <v>0.03995627136944394</v>
+        <v>0.04719786892758936</v>
       </c>
       <c r="T121" t="n">
-        <v>0.03995627136944394</v>
+        <v>0.04719786892758936</v>
       </c>
       <c r="U121" t="n">
-        <v>0.03995627136944394</v>
+        <v>0.04719786892758936</v>
       </c>
       <c r="V121" t="n">
-        <v>0.03995627136944394</v>
+        <v>0.04719786892758936</v>
       </c>
       <c r="W121" t="n">
-        <v>0.03995627136944394</v>
+        <v>0.04719786892758936</v>
       </c>
       <c r="X121" t="n">
-        <v>0.03995627136944394</v>
+        <v>0.04719786892758936</v>
       </c>
       <c r="Y121" t="n">
-        <v>0.03995627136944394</v>
+        <v>0.04719786892758936</v>
       </c>
       <c r="Z121" t="n">
-        <v>0.03995627136944394</v>
+        <v>0.04719786892758936</v>
       </c>
       <c r="AA121" t="n">
-        <v>0.03995627136944394</v>
+        <v>0.04719786892758936</v>
       </c>
       <c r="AB121" t="n">
-        <v>0.03995627136944394</v>
+        <v>0.04719786892758936</v>
       </c>
       <c r="AC121" t="n">
-        <v>0.03995627136944394</v>
+        <v>0.04719786892758936</v>
       </c>
       <c r="AD121" t="n">
-        <v>0.01434143056871148</v>
+        <v>0.01447482398444818</v>
       </c>
       <c r="AE121" t="n">
-        <v>0.01434143056871148</v>
+        <v>0.01447482398444818</v>
       </c>
       <c r="AF121" t="n">
-        <v>0.01434143056871148</v>
+        <v>0.01447482398444818</v>
       </c>
       <c r="AG121" t="n">
-        <v>0.08082401854206432</v>
+        <v>0.08157578398521435</v>
       </c>
       <c r="AH121" t="n">
-        <v>0.08082401854206432</v>
+        <v>0.08157578398521435</v>
       </c>
       <c r="AI121" t="n">
-        <v>0.08082401854206432</v>
+        <v>0.08157578398521435</v>
       </c>
       <c r="AJ121" t="n">
-        <v>0.08082401854206432</v>
+        <v>0.08157578398521435</v>
       </c>
       <c r="AK121" t="n">
-        <v>0.08082401854206432</v>
+        <v>0.08157578398521435</v>
       </c>
       <c r="AL121" t="n">
-        <v>0.08082401854206432</v>
+        <v>0.08157578398521435</v>
       </c>
       <c r="AM121" t="n">
-        <v>0.01434143056871148</v>
+        <v>0.01447482398444818</v>
       </c>
       <c r="AN121" t="n">
-        <v>0.01434143056871148</v>
+        <v>0.01447482398444818</v>
       </c>
       <c r="AO121" t="n">
-        <v>0.01434143056871148</v>
+        <v>0.01447482398444818</v>
       </c>
     </row>
     <row r="122">
@@ -15287,7 +15287,7 @@
       <c r="D125" t="inlineStr"/>
       <c r="E125" t="inlineStr"/>
       <c r="F125" t="n">
-        <v>0.2589285714285715</v>
+        <v>0.5178571428571429</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
@@ -15316,7 +15316,7 @@
         <v>1</v>
       </c>
       <c r="Q125" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R125" t="n">
         <v>0.05</v>
@@ -16834,7 +16834,7 @@
       <c r="D138" t="inlineStr"/>
       <c r="E138" t="inlineStr"/>
       <c r="F138" t="n">
-        <v>0.5434179357021997</v>
+        <v>0.8479864636209813</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
@@ -16863,7 +16863,7 @@
         <v>1</v>
       </c>
       <c r="Q138" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R138" t="n">
         <v>0.05</v>
@@ -16953,7 +16953,7 @@
       <c r="D139" t="inlineStr"/>
       <c r="E139" t="inlineStr"/>
       <c r="F139" t="n">
-        <v>2.483611111111111</v>
+        <v>2.5085</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -16962,13 +16962,13 @@
         <v>0.5099999999999999</v>
       </c>
       <c r="I139" t="n">
-        <v>0.05304497525026338</v>
+        <v>0.05301955579088971</v>
       </c>
       <c r="J139" t="n">
         <v>1</v>
       </c>
       <c r="K139" t="n">
-        <v>26.64011862555982</v>
+        <v>26.52625088846592</v>
       </c>
       <c r="L139" t="n">
         <v>0.15</v>
@@ -16982,79 +16982,79 @@
         <v>1</v>
       </c>
       <c r="Q139" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="R139" t="n">
-        <v>0.05304497525026338</v>
+        <v>0.05301955579088971</v>
       </c>
       <c r="S139" t="n">
-        <v>0.05304497525026338</v>
+        <v>0.05301955579088971</v>
       </c>
       <c r="T139" t="n">
-        <v>0.05304497525026338</v>
+        <v>0.05301955579088971</v>
       </c>
       <c r="U139" t="n">
-        <v>0.05304497525026338</v>
+        <v>0.05301955579088971</v>
       </c>
       <c r="V139" t="n">
-        <v>0.05304497525026338</v>
+        <v>0.05301955579088971</v>
       </c>
       <c r="W139" t="n">
-        <v>0.05304497525026338</v>
+        <v>0.05301955579088971</v>
       </c>
       <c r="X139" t="n">
-        <v>0.05304497525026338</v>
+        <v>0.05301955579088971</v>
       </c>
       <c r="Y139" t="n">
-        <v>0.05304497525026338</v>
+        <v>0.05301955579088971</v>
       </c>
       <c r="Z139" t="n">
-        <v>0.05304497525026338</v>
+        <v>0.05301955579088971</v>
       </c>
       <c r="AA139" t="n">
-        <v>0.05304497525026338</v>
+        <v>0.05301955579088971</v>
       </c>
       <c r="AB139" t="n">
-        <v>0.05304497525026338</v>
+        <v>0.05301955579088971</v>
       </c>
       <c r="AC139" t="n">
-        <v>0.05304497525026338</v>
+        <v>0.05301955579088971</v>
       </c>
       <c r="AD139" t="n">
-        <v>0.02195614172436249</v>
+        <v>0.02186229468829609</v>
       </c>
       <c r="AE139" t="n">
-        <v>0.02195614172436249</v>
+        <v>0.02186229468829609</v>
       </c>
       <c r="AF139" t="n">
-        <v>0.02195614172436249</v>
+        <v>0.02186229468829609</v>
       </c>
       <c r="AG139" t="n">
-        <v>0.1237382559110702</v>
+        <v>0.1232093620502516</v>
       </c>
       <c r="AH139" t="n">
-        <v>0.1237382559110702</v>
+        <v>0.1232093620502516</v>
       </c>
       <c r="AI139" t="n">
-        <v>0.1237382559110702</v>
+        <v>0.1232093620502516</v>
       </c>
       <c r="AJ139" t="n">
-        <v>0.1237382559110702</v>
+        <v>0.1232093620502516</v>
       </c>
       <c r="AK139" t="n">
-        <v>0.1237382559110702</v>
+        <v>0.1232093620502516</v>
       </c>
       <c r="AL139" t="n">
-        <v>0.1237382559110702</v>
+        <v>0.1232093620502516</v>
       </c>
       <c r="AM139" t="n">
-        <v>0.02195614172436249</v>
+        <v>0.02186229468829609</v>
       </c>
       <c r="AN139" t="n">
-        <v>0.02195614172436249</v>
+        <v>0.02186229468829609</v>
       </c>
       <c r="AO139" t="n">
-        <v>0.02195614172436249</v>
+        <v>0.02186229468829609</v>
       </c>
     </row>
     <row r="140">
@@ -17310,7 +17310,7 @@
       <c r="D142" t="inlineStr"/>
       <c r="E142" t="inlineStr"/>
       <c r="F142" t="n">
-        <v>5.917110874200427</v>
+        <v>6.247601279317697</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
@@ -17319,13 +17319,13 @@
         <v>0.48</v>
       </c>
       <c r="I142" t="n">
-        <v>0.05982025894617322</v>
+        <v>0.05936870635897658</v>
       </c>
       <c r="J142" t="n">
         <v>1</v>
       </c>
       <c r="K142" t="n">
-        <v>26.45641023756636</v>
+        <v>26.48140544033504</v>
       </c>
       <c r="L142" t="n">
         <v>0.15</v>
@@ -17339,79 +17339,79 @@
         <v>1</v>
       </c>
       <c r="Q142" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="R142" t="n">
-        <v>0.05982025894617322</v>
+        <v>0.05936870635897658</v>
       </c>
       <c r="S142" t="n">
-        <v>0.05982025894617322</v>
+        <v>0.05936870635897658</v>
       </c>
       <c r="T142" t="n">
-        <v>0.05982025894617322</v>
+        <v>0.05936870635897658</v>
       </c>
       <c r="U142" t="n">
-        <v>0.05982025894617322</v>
+        <v>0.05936870635897658</v>
       </c>
       <c r="V142" t="n">
-        <v>0.05982025894617322</v>
+        <v>0.05936870635897658</v>
       </c>
       <c r="W142" t="n">
-        <v>0.05982025894617322</v>
+        <v>0.05936870635897658</v>
       </c>
       <c r="X142" t="n">
-        <v>0.05982025894617322</v>
+        <v>0.05936870635897658</v>
       </c>
       <c r="Y142" t="n">
-        <v>0.05982025894617322</v>
+        <v>0.05936870635897658</v>
       </c>
       <c r="Z142" t="n">
-        <v>0.05982025894617322</v>
+        <v>0.05936870635897658</v>
       </c>
       <c r="AA142" t="n">
-        <v>0.05982025894617322</v>
+        <v>0.05936870635897658</v>
       </c>
       <c r="AB142" t="n">
-        <v>0.05982025894617322</v>
+        <v>0.05936870635897658</v>
       </c>
       <c r="AC142" t="n">
-        <v>0.05982025894617322</v>
+        <v>0.05936870635897658</v>
       </c>
       <c r="AD142" t="n">
-        <v>0.02180473371227997</v>
+        <v>0.02182533415412229</v>
       </c>
       <c r="AE142" t="n">
-        <v>0.02180473371227997</v>
+        <v>0.02182533415412229</v>
       </c>
       <c r="AF142" t="n">
-        <v>0.02180473371227997</v>
+        <v>0.02182533415412229</v>
       </c>
       <c r="AG142" t="n">
-        <v>0.1228849655843246</v>
+        <v>0.1230010635206819</v>
       </c>
       <c r="AH142" t="n">
-        <v>0.1228849655843246</v>
+        <v>0.1230010635206819</v>
       </c>
       <c r="AI142" t="n">
-        <v>0.1228849655843246</v>
+        <v>0.1230010635206819</v>
       </c>
       <c r="AJ142" t="n">
-        <v>0.1228849655843246</v>
+        <v>0.1230010635206819</v>
       </c>
       <c r="AK142" t="n">
-        <v>0.1228849655843246</v>
+        <v>0.1230010635206819</v>
       </c>
       <c r="AL142" t="n">
-        <v>0.1228849655843246</v>
+        <v>0.1230010635206819</v>
       </c>
       <c r="AM142" t="n">
-        <v>0.02180473371227997</v>
+        <v>0.02182533415412229</v>
       </c>
       <c r="AN142" t="n">
-        <v>0.02180473371227997</v>
+        <v>0.02182533415412229</v>
       </c>
       <c r="AO142" t="n">
-        <v>0.02180473371227997</v>
+        <v>0.02182533415412229</v>
       </c>
     </row>
     <row r="143">
@@ -18262,7 +18262,7 @@
       <c r="D150" t="inlineStr"/>
       <c r="E150" t="inlineStr"/>
       <c r="F150" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G150" t="n">
         <v>0</v>
@@ -18291,7 +18291,7 @@
         <v>1</v>
       </c>
       <c r="Q150" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R150" t="n">
         <v>0.08000000000000002</v>
@@ -18619,7 +18619,7 @@
       <c r="D153" t="inlineStr"/>
       <c r="E153" t="inlineStr"/>
       <c r="F153" t="n">
-        <v>0.6915322580645161</v>
+        <v>1.377016129032258</v>
       </c>
       <c r="G153" t="n">
         <v>0</v>
@@ -18648,7 +18648,7 @@
         <v>1</v>
       </c>
       <c r="Q153" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R153" t="n">
         <v>0.08</v>
@@ -19452,7 +19452,7 @@
       <c r="D160" t="inlineStr"/>
       <c r="E160" t="inlineStr"/>
       <c r="F160" t="n">
-        <v>0.7993333333333333</v>
+        <v>1.399333333333333</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
@@ -19481,7 +19481,7 @@
         <v>1</v>
       </c>
       <c r="Q160" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R160" t="n">
         <v>0.05</v>
@@ -19571,7 +19571,7 @@
       <c r="D161" t="inlineStr"/>
       <c r="E161" t="inlineStr"/>
       <c r="F161" t="n">
-        <v>1.369622641509434</v>
+        <v>2.077169811320755</v>
       </c>
       <c r="G161" t="n">
         <v>0</v>
@@ -19600,7 +19600,7 @@
         <v>1</v>
       </c>
       <c r="Q161" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R161" t="n">
         <v>0.08</v>
@@ -19928,7 +19928,7 @@
       <c r="D164" t="inlineStr"/>
       <c r="E164" t="inlineStr"/>
       <c r="F164" t="n">
-        <v>1.261818181818182</v>
+        <v>1.283636363636364</v>
       </c>
       <c r="G164" t="n">
         <v>0</v>
@@ -19957,7 +19957,7 @@
         <v>0</v>
       </c>
       <c r="Q164" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R164" t="n">
         <v>0.05</v>
@@ -20523,7 +20523,7 @@
       <c r="D169" t="inlineStr"/>
       <c r="E169" t="inlineStr"/>
       <c r="F169" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G169" t="n">
         <v>0</v>
@@ -20552,7 +20552,7 @@
         <v>0</v>
       </c>
       <c r="Q169" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="R169" t="n">
         <v>0.08</v>
@@ -20642,7 +20642,7 @@
       <c r="D170" t="inlineStr"/>
       <c r="E170" t="inlineStr"/>
       <c r="F170" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="G170" t="n">
         <v>0</v>
@@ -20671,7 +20671,7 @@
         <v>0</v>
       </c>
       <c r="Q170" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R170" t="n">
         <v>0.08</v>
@@ -20880,13 +20880,13 @@
       <c r="D172" t="inlineStr"/>
       <c r="E172" t="inlineStr"/>
       <c r="F172" t="n">
-        <v>2.473127659574468</v>
+        <v>2.833127659574468</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
       </c>
       <c r="H172" t="n">
-        <v>0.5722828593389701</v>
+        <v>0.5704036458333334</v>
       </c>
       <c r="I172" t="n">
         <v>0.05</v>
@@ -20909,7 +20909,7 @@
         <v>0</v>
       </c>
       <c r="Q172" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R172" t="n">
         <v>0.05</v>
@@ -21356,13 +21356,13 @@
       <c r="D176" t="inlineStr"/>
       <c r="E176" t="inlineStr"/>
       <c r="F176" t="n">
-        <v>1.243105828220859</v>
+        <v>1.42454754601227</v>
       </c>
       <c r="G176" t="n">
         <v>0</v>
       </c>
       <c r="H176" t="n">
-        <v>0.5758287841191067</v>
+        <v>0.5762602892102335</v>
       </c>
       <c r="I176" t="n">
         <v>0.05</v>
@@ -21385,7 +21385,7 @@
         <v>0</v>
       </c>
       <c r="Q176" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="R176" t="n">
         <v>0.05</v>
@@ -21475,7 +21475,7 @@
       <c r="D177" t="inlineStr"/>
       <c r="E177" t="inlineStr"/>
       <c r="F177" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="G177" t="n">
         <v>0</v>
@@ -21504,7 +21504,7 @@
         <v>0</v>
       </c>
       <c r="Q177" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R177" t="n">
         <v>0.075</v>
@@ -22793,7 +22793,7 @@
         <v>0.35</v>
       </c>
       <c r="I188" t="n">
-        <v>0.02584467754506221</v>
+        <v>0.0258446775450622</v>
       </c>
       <c r="J188" t="n">
         <v>0.3535523603975673</v>
@@ -22816,40 +22816,40 @@
         <v>14</v>
       </c>
       <c r="R188" t="n">
-        <v>0.02584467754506221</v>
+        <v>0.0258446775450622</v>
       </c>
       <c r="S188" t="n">
-        <v>0.02584467754506221</v>
+        <v>0.0258446775450622</v>
       </c>
       <c r="T188" t="n">
-        <v>0.02584467754506221</v>
+        <v>0.0258446775450622</v>
       </c>
       <c r="U188" t="n">
-        <v>0.02584467754506221</v>
+        <v>0.0258446775450622</v>
       </c>
       <c r="V188" t="n">
-        <v>0.02584467754506221</v>
+        <v>0.0258446775450622</v>
       </c>
       <c r="W188" t="n">
-        <v>0.02584467754506221</v>
+        <v>0.0258446775450622</v>
       </c>
       <c r="X188" t="n">
-        <v>0.02584467754506221</v>
+        <v>0.0258446775450622</v>
       </c>
       <c r="Y188" t="n">
-        <v>0.02584467754506221</v>
+        <v>0.0258446775450622</v>
       </c>
       <c r="Z188" t="n">
-        <v>0.02584467754506221</v>
+        <v>0.0258446775450622</v>
       </c>
       <c r="AA188" t="n">
-        <v>0.02584467754506221</v>
+        <v>0.0258446775450622</v>
       </c>
       <c r="AB188" t="n">
-        <v>0.02584467754506221</v>
+        <v>0.0258446775450622</v>
       </c>
       <c r="AC188" t="n">
-        <v>0.02584467754506221</v>
+        <v>0.0258446775450622</v>
       </c>
       <c r="AD188" t="n">
         <v>0.006119175468419434</v>
@@ -23260,7 +23260,7 @@
       <c r="D192" t="inlineStr"/>
       <c r="E192" t="inlineStr"/>
       <c r="F192" t="n">
-        <v>1.56415770609319</v>
+        <v>1.96415770609319</v>
       </c>
       <c r="G192" t="n">
         <v>0</v>
@@ -23289,7 +23289,7 @@
         <v>0</v>
       </c>
       <c r="Q192" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R192" t="n">
         <v>0.05</v>
@@ -23974,22 +23974,22 @@
       <c r="D198" t="inlineStr"/>
       <c r="E198" t="inlineStr"/>
       <c r="F198" t="n">
-        <v>2.589317507418397</v>
+        <v>2.989317507418397</v>
       </c>
       <c r="G198" t="n">
         <v>0</v>
       </c>
       <c r="H198" t="n">
-        <v>0.33</v>
+        <v>0.3300000000000001</v>
       </c>
       <c r="I198" t="n">
-        <v>0.05</v>
+        <v>0.05000000000000001</v>
       </c>
       <c r="J198" t="n">
         <v>7</v>
       </c>
       <c r="K198" t="n">
-        <v>35.68255283878989</v>
+        <v>39.68189180434079</v>
       </c>
       <c r="L198" t="n">
         <v>0.15</v>
@@ -24003,79 +24003,79 @@
         <v>0</v>
       </c>
       <c r="Q198" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R198" t="n">
-        <v>0.05</v>
+        <v>0.05000000000000001</v>
       </c>
       <c r="S198" t="n">
-        <v>0.05</v>
+        <v>0.05000000000000001</v>
       </c>
       <c r="T198" t="n">
-        <v>0.05</v>
+        <v>0.05000000000000001</v>
       </c>
       <c r="U198" t="n">
-        <v>0.05</v>
+        <v>0.05000000000000001</v>
       </c>
       <c r="V198" t="n">
-        <v>0.05</v>
+        <v>0.05000000000000001</v>
       </c>
       <c r="W198" t="n">
-        <v>0.05</v>
+        <v>0.05000000000000001</v>
       </c>
       <c r="X198" t="n">
-        <v>0.05</v>
+        <v>0.05000000000000001</v>
       </c>
       <c r="Y198" t="n">
-        <v>0.05</v>
+        <v>0.05000000000000001</v>
       </c>
       <c r="Z198" t="n">
-        <v>0.05</v>
+        <v>0.05000000000000001</v>
       </c>
       <c r="AA198" t="n">
-        <v>0.05</v>
+        <v>0.05000000000000001</v>
       </c>
       <c r="AB198" t="n">
-        <v>0.05</v>
+        <v>0.05000000000000001</v>
       </c>
       <c r="AC198" t="n">
-        <v>0.05</v>
+        <v>0.05000000000000001</v>
       </c>
       <c r="AD198" t="n">
-        <v>0.02940869739460705</v>
+        <v>0.03270485588269845</v>
       </c>
       <c r="AE198" t="n">
-        <v>0.02940869739460705</v>
+        <v>0.03270485588269845</v>
       </c>
       <c r="AF198" t="n">
-        <v>0.02940869739460705</v>
+        <v>0.03270485588269845</v>
       </c>
       <c r="AG198" t="n">
-        <v>0.1657386334042153</v>
+        <v>0.1843147979983042</v>
       </c>
       <c r="AH198" t="n">
-        <v>0.1657386334042153</v>
+        <v>0.1843147979983042</v>
       </c>
       <c r="AI198" t="n">
-        <v>0.1657386334042153</v>
+        <v>0.1843147979983042</v>
       </c>
       <c r="AJ198" t="n">
-        <v>0.1657386334042153</v>
+        <v>0.1843147979983042</v>
       </c>
       <c r="AK198" t="n">
-        <v>0.1657386334042153</v>
+        <v>0.1843147979983042</v>
       </c>
       <c r="AL198" t="n">
-        <v>0.1657386334042153</v>
+        <v>0.1843147979983042</v>
       </c>
       <c r="AM198" t="n">
-        <v>0.02940869739460705</v>
+        <v>0.03270485588269845</v>
       </c>
       <c r="AN198" t="n">
-        <v>0.02940869739460705</v>
+        <v>0.03270485588269845</v>
       </c>
       <c r="AO198" t="n">
-        <v>0.02940869739460705</v>
+        <v>0.03270485588269845</v>
       </c>
     </row>
     <row r="199">
@@ -24212,7 +24212,7 @@
       <c r="D200" t="inlineStr"/>
       <c r="E200" t="inlineStr"/>
       <c r="F200" t="n">
-        <v>0.4803252032520325</v>
+        <v>0.8632520325203252</v>
       </c>
       <c r="G200" t="n">
         <v>0</v>
@@ -24221,7 +24221,7 @@
         <v>0.6</v>
       </c>
       <c r="I200" t="n">
-        <v>0.009999999999999998</v>
+        <v>0.01</v>
       </c>
       <c r="J200" t="n">
         <v>1</v>
@@ -24241,43 +24241,43 @@
         <v>0</v>
       </c>
       <c r="Q200" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R200" t="n">
-        <v>0.009999999999999998</v>
+        <v>0.01</v>
       </c>
       <c r="S200" t="n">
-        <v>0.009999999999999998</v>
+        <v>0.01</v>
       </c>
       <c r="T200" t="n">
-        <v>0.009999999999999998</v>
+        <v>0.01</v>
       </c>
       <c r="U200" t="n">
-        <v>0.009999999999999998</v>
+        <v>0.01</v>
       </c>
       <c r="V200" t="n">
-        <v>0.009999999999999998</v>
+        <v>0.01</v>
       </c>
       <c r="W200" t="n">
-        <v>0.009999999999999998</v>
+        <v>0.01</v>
       </c>
       <c r="X200" t="n">
-        <v>0.009999999999999998</v>
+        <v>0.01</v>
       </c>
       <c r="Y200" t="n">
-        <v>0.009999999999999998</v>
+        <v>0.01</v>
       </c>
       <c r="Z200" t="n">
-        <v>0.009999999999999998</v>
+        <v>0.01</v>
       </c>
       <c r="AA200" t="n">
-        <v>0.009999999999999998</v>
+        <v>0.01</v>
       </c>
       <c r="AB200" t="n">
-        <v>0.009999999999999998</v>
+        <v>0.01</v>
       </c>
       <c r="AC200" t="n">
-        <v>0.009999999999999998</v>
+        <v>0.01</v>
       </c>
       <c r="AD200" t="n">
         <v>0</v>
@@ -24807,7 +24807,7 @@
       <c r="D205" t="inlineStr"/>
       <c r="E205" t="inlineStr"/>
       <c r="F205" t="n">
-        <v>0.46</v>
+        <v>0.5171428571428572</v>
       </c>
       <c r="G205" t="n">
         <v>0</v>
@@ -24836,7 +24836,7 @@
         <v>0</v>
       </c>
       <c r="Q205" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R205" t="n">
         <v>0.05</v>
@@ -24926,7 +24926,7 @@
       <c r="D206" t="inlineStr"/>
       <c r="E206" t="inlineStr"/>
       <c r="F206" t="n">
-        <v>1.679</v>
+        <v>2.308857142857143</v>
       </c>
       <c r="G206" t="n">
         <v>0</v>
@@ -24935,7 +24935,7 @@
         <v>0.33</v>
       </c>
       <c r="I206" t="n">
-        <v>0.05000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="J206" t="n">
         <v>7</v>
@@ -24955,43 +24955,43 @@
         <v>0</v>
       </c>
       <c r="Q206" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="R206" t="n">
-        <v>0.05000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="S206" t="n">
-        <v>0.05000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="T206" t="n">
-        <v>0.05000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="U206" t="n">
-        <v>0.05000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="V206" t="n">
-        <v>0.05000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="W206" t="n">
-        <v>0.05000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="X206" t="n">
-        <v>0.05000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="Y206" t="n">
-        <v>0.05000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="Z206" t="n">
-        <v>0.05000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="AA206" t="n">
-        <v>0.05000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="AB206" t="n">
-        <v>0.05000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="AC206" t="n">
-        <v>0.05000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="AD206" t="n">
         <v>0</v>
@@ -25164,16 +25164,16 @@
       <c r="D208" t="inlineStr"/>
       <c r="E208" t="inlineStr"/>
       <c r="F208" t="n">
-        <v>0.07142857142857142</v>
+        <v>0.08928571428571429</v>
       </c>
       <c r="G208" t="n">
         <v>0</v>
       </c>
       <c r="H208" t="n">
-        <v>0.5178947368421053</v>
+        <v>0.5483443708609272</v>
       </c>
       <c r="I208" t="n">
-        <v>0.03546342490562927</v>
+        <v>0.04085447262274689</v>
       </c>
       <c r="J208" t="n">
         <v>1</v>
@@ -25193,43 +25193,43 @@
         <v>0</v>
       </c>
       <c r="Q208" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R208" t="n">
-        <v>0.03546342490562927</v>
+        <v>0.04085447262274689</v>
       </c>
       <c r="S208" t="n">
-        <v>0.03546342490562927</v>
+        <v>0.04085447262274689</v>
       </c>
       <c r="T208" t="n">
-        <v>0.03546342490562927</v>
+        <v>0.04085447262274689</v>
       </c>
       <c r="U208" t="n">
-        <v>0.03546342490562927</v>
+        <v>0.04085447262274689</v>
       </c>
       <c r="V208" t="n">
-        <v>0.03546342490562927</v>
+        <v>0.04085447262274689</v>
       </c>
       <c r="W208" t="n">
-        <v>0.03546342490562927</v>
+        <v>0.04085447262274689</v>
       </c>
       <c r="X208" t="n">
-        <v>0.03546342490562927</v>
+        <v>0.04085447262274689</v>
       </c>
       <c r="Y208" t="n">
-        <v>0.03546342490562927</v>
+        <v>0.04085447262274689</v>
       </c>
       <c r="Z208" t="n">
-        <v>0.03546342490562927</v>
+        <v>0.04085447262274689</v>
       </c>
       <c r="AA208" t="n">
-        <v>0.03546342490562927</v>
+        <v>0.04085447262274689</v>
       </c>
       <c r="AB208" t="n">
-        <v>0.03546342490562927</v>
+        <v>0.04085447262274689</v>
       </c>
       <c r="AC208" t="n">
-        <v>0.03546342490562927</v>
+        <v>0.04085447262274689</v>
       </c>
       <c r="AD208" t="n">
         <v>0.02225274725274725</v>
@@ -27255,40 +27255,40 @@
         <v>0.01155824887362251</v>
       </c>
       <c r="AD225" t="n">
-        <v>0.003494954742146343</v>
+        <v>0.003494954742146342</v>
       </c>
       <c r="AE225" t="n">
-        <v>0.003494954742146343</v>
+        <v>0.003494954742146342</v>
       </c>
       <c r="AF225" t="n">
-        <v>0.003494954742146343</v>
+        <v>0.003494954742146342</v>
       </c>
       <c r="AG225" t="n">
-        <v>0.09488479910890364</v>
+        <v>0.09488479910890363</v>
       </c>
       <c r="AH225" t="n">
-        <v>0.09488479910890364</v>
+        <v>0.09488479910890363</v>
       </c>
       <c r="AI225" t="n">
-        <v>0.09488479910890364</v>
+        <v>0.09488479910890363</v>
       </c>
       <c r="AJ225" t="n">
-        <v>0.09488479910890364</v>
+        <v>0.09488479910890363</v>
       </c>
       <c r="AK225" t="n">
-        <v>0.09488479910890364</v>
+        <v>0.09488479910890363</v>
       </c>
       <c r="AL225" t="n">
-        <v>0.09488479910890364</v>
+        <v>0.09488479910890363</v>
       </c>
       <c r="AM225" t="n">
-        <v>0.003494954742146343</v>
+        <v>0.003494954742146342</v>
       </c>
       <c r="AN225" t="n">
-        <v>0.003494954742146343</v>
+        <v>0.003494954742146342</v>
       </c>
       <c r="AO225" t="n">
-        <v>0.003494954742146343</v>
+        <v>0.003494954742146342</v>
       </c>
     </row>
     <row r="226">
@@ -27306,7 +27306,7 @@
       <c r="D226" t="inlineStr"/>
       <c r="E226" t="inlineStr"/>
       <c r="F226" t="n">
-        <v>1.138095238095238</v>
+        <v>9.647619047619047</v>
       </c>
       <c r="G226" t="n">
         <v>0</v>
@@ -27335,7 +27335,7 @@
         <v>0</v>
       </c>
       <c r="Q226" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="R226" t="n">
         <v>0.05</v>
@@ -27374,13 +27374,13 @@
         <v>0.05</v>
       </c>
       <c r="AD226" t="n">
-        <v>0.02225274725274725</v>
+        <v>0.02225274725274726</v>
       </c>
       <c r="AE226" t="n">
-        <v>0.02225274725274725</v>
+        <v>0.02225274725274726</v>
       </c>
       <c r="AF226" t="n">
-        <v>0.02225274725274725</v>
+        <v>0.02225274725274726</v>
       </c>
       <c r="AG226" t="n">
         <v>0.1254098360655738</v>
@@ -27401,13 +27401,13 @@
         <v>0.1254098360655738</v>
       </c>
       <c r="AM226" t="n">
-        <v>0.02225274725274725</v>
+        <v>0.02225274725274726</v>
       </c>
       <c r="AN226" t="n">
-        <v>0.02225274725274725</v>
+        <v>0.02225274725274726</v>
       </c>
       <c r="AO226" t="n">
-        <v>0.02225274725274725</v>
+        <v>0.02225274725274726</v>
       </c>
     </row>
     <row r="227">
@@ -27425,13 +27425,13 @@
       <c r="D227" t="inlineStr"/>
       <c r="E227" t="inlineStr"/>
       <c r="F227" t="n">
-        <v>1.805620685620686</v>
+        <v>5.743376623376624</v>
       </c>
       <c r="G227" t="n">
         <v>0</v>
       </c>
       <c r="H227" t="n">
-        <v>0.6000000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="I227" t="n">
         <v>0.05</v>
@@ -27440,7 +27440,7 @@
         <v>1</v>
       </c>
       <c r="K227" t="n">
-        <v>27.00000000000001</v>
+        <v>27</v>
       </c>
       <c r="L227" t="n">
         <v>0.15</v>
@@ -27454,7 +27454,7 @@
         <v>0</v>
       </c>
       <c r="Q227" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="R227" t="n">
         <v>0.05</v>
@@ -27493,13 +27493,13 @@
         <v>0.05</v>
       </c>
       <c r="AD227" t="n">
-        <v>0.02225274725274726</v>
+        <v>0.02225274725274725</v>
       </c>
       <c r="AE227" t="n">
-        <v>0.02225274725274726</v>
+        <v>0.02225274725274725</v>
       </c>
       <c r="AF227" t="n">
-        <v>0.02225274725274726</v>
+        <v>0.02225274725274725</v>
       </c>
       <c r="AG227" t="n">
         <v>0.1254098360655738</v>
@@ -27520,13 +27520,13 @@
         <v>0.1254098360655738</v>
       </c>
       <c r="AM227" t="n">
-        <v>0.02225274725274726</v>
+        <v>0.02225274725274725</v>
       </c>
       <c r="AN227" t="n">
-        <v>0.02225274725274726</v>
+        <v>0.02225274725274725</v>
       </c>
       <c r="AO227" t="n">
-        <v>0.02225274725274726</v>
+        <v>0.02225274725274725</v>
       </c>
     </row>
     <row r="228">
@@ -27544,16 +27544,16 @@
       <c r="D228" t="inlineStr"/>
       <c r="E228" t="inlineStr"/>
       <c r="F228" t="n">
-        <v>2.65620253164557</v>
+        <v>14.52050632911392</v>
       </c>
       <c r="G228" t="n">
         <v>0</v>
       </c>
       <c r="H228" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5599999999999998</v>
       </c>
       <c r="I228" t="n">
-        <v>0.05</v>
+        <v>0.04999999999999999</v>
       </c>
       <c r="J228" t="n">
         <v>1</v>
@@ -27573,43 +27573,43 @@
         <v>0</v>
       </c>
       <c r="Q228" t="n">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="R228" t="n">
-        <v>0.05</v>
+        <v>0.04999999999999999</v>
       </c>
       <c r="S228" t="n">
-        <v>0.05</v>
+        <v>0.04999999999999999</v>
       </c>
       <c r="T228" t="n">
-        <v>0.05</v>
+        <v>0.04999999999999999</v>
       </c>
       <c r="U228" t="n">
-        <v>0.05</v>
+        <v>0.04999999999999999</v>
       </c>
       <c r="V228" t="n">
-        <v>0.05</v>
+        <v>0.04999999999999999</v>
       </c>
       <c r="W228" t="n">
-        <v>0.05</v>
+        <v>0.04999999999999999</v>
       </c>
       <c r="X228" t="n">
-        <v>0.05</v>
+        <v>0.04999999999999999</v>
       </c>
       <c r="Y228" t="n">
-        <v>0.05</v>
+        <v>0.04999999999999999</v>
       </c>
       <c r="Z228" t="n">
-        <v>0.05</v>
+        <v>0.04999999999999999</v>
       </c>
       <c r="AA228" t="n">
-        <v>0.05</v>
+        <v>0.04999999999999999</v>
       </c>
       <c r="AB228" t="n">
-        <v>0.05</v>
+        <v>0.04999999999999999</v>
       </c>
       <c r="AC228" t="n">
-        <v>0.05</v>
+        <v>0.04999999999999999</v>
       </c>
       <c r="AD228" t="n">
         <v>0.02225274725274725</v>
@@ -27663,13 +27663,13 @@
       <c r="D229" t="inlineStr"/>
       <c r="E229" t="inlineStr"/>
       <c r="F229" t="n">
-        <v>1.060259125451601</v>
+        <v>1.843864457456085</v>
       </c>
       <c r="G229" t="n">
         <v>0</v>
       </c>
       <c r="H229" t="n">
-        <v>0.3599999999999999</v>
+        <v>0.36</v>
       </c>
       <c r="I229" t="n">
         <v>0.08</v>
@@ -27692,7 +27692,7 @@
         <v>0</v>
       </c>
       <c r="Q229" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="R229" t="n">
         <v>0.08</v>
@@ -27782,16 +27782,16 @@
       <c r="D230" t="inlineStr"/>
       <c r="E230" t="inlineStr"/>
       <c r="F230" t="n">
-        <v>0.7678389261744967</v>
+        <v>4.175892617449664</v>
       </c>
       <c r="G230" t="n">
         <v>0</v>
       </c>
       <c r="H230" t="n">
-        <v>0.41</v>
+        <v>0.4099999999999999</v>
       </c>
       <c r="I230" t="n">
-        <v>0.08</v>
+        <v>0.07999999999999997</v>
       </c>
       <c r="J230" t="n">
         <v>1</v>
@@ -27811,52 +27811,52 @@
         <v>0</v>
       </c>
       <c r="Q230" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="R230" t="n">
-        <v>0.08</v>
+        <v>0.07999999999999997</v>
       </c>
       <c r="S230" t="n">
-        <v>0.08</v>
+        <v>0.07999999999999997</v>
       </c>
       <c r="T230" t="n">
-        <v>0.08</v>
+        <v>0.07999999999999997</v>
       </c>
       <c r="U230" t="n">
-        <v>0.08</v>
+        <v>0.07999999999999997</v>
       </c>
       <c r="V230" t="n">
-        <v>0.08</v>
+        <v>0.07999999999999997</v>
       </c>
       <c r="W230" t="n">
-        <v>0.08</v>
+        <v>0.07999999999999997</v>
       </c>
       <c r="X230" t="n">
-        <v>0.08</v>
+        <v>0.07999999999999997</v>
       </c>
       <c r="Y230" t="n">
-        <v>0.08</v>
+        <v>0.07999999999999997</v>
       </c>
       <c r="Z230" t="n">
-        <v>0.08</v>
+        <v>0.07999999999999997</v>
       </c>
       <c r="AA230" t="n">
-        <v>0.08</v>
+        <v>0.07999999999999997</v>
       </c>
       <c r="AB230" t="n">
-        <v>0.08</v>
+        <v>0.07999999999999997</v>
       </c>
       <c r="AC230" t="n">
-        <v>0.08</v>
+        <v>0.07999999999999997</v>
       </c>
       <c r="AD230" t="n">
-        <v>0.02225274725274725</v>
+        <v>0.02225274725274726</v>
       </c>
       <c r="AE230" t="n">
-        <v>0.02225274725274725</v>
+        <v>0.02225274725274726</v>
       </c>
       <c r="AF230" t="n">
-        <v>0.02225274725274725</v>
+        <v>0.02225274725274726</v>
       </c>
       <c r="AG230" t="n">
         <v>0.1254098360655738</v>
@@ -27877,13 +27877,13 @@
         <v>0.1254098360655738</v>
       </c>
       <c r="AM230" t="n">
-        <v>0.02225274725274725</v>
+        <v>0.02225274725274726</v>
       </c>
       <c r="AN230" t="n">
-        <v>0.02225274725274725</v>
+        <v>0.02225274725274726</v>
       </c>
       <c r="AO230" t="n">
-        <v>0.02225274725274725</v>
+        <v>0.02225274725274726</v>
       </c>
     </row>
     <row r="231">
@@ -28020,13 +28020,13 @@
       <c r="D232" t="inlineStr"/>
       <c r="E232" t="inlineStr"/>
       <c r="F232" t="n">
-        <v>0.6933884297520662</v>
+        <v>2.480165289256199</v>
       </c>
       <c r="G232" t="n">
         <v>0</v>
       </c>
       <c r="H232" t="n">
-        <v>0.33</v>
+        <v>0.3300000000000001</v>
       </c>
       <c r="I232" t="n">
         <v>0.05</v>
@@ -28049,7 +28049,7 @@
         <v>0</v>
       </c>
       <c r="Q232" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="R232" t="n">
         <v>0.05</v>
@@ -28139,7 +28139,7 @@
       <c r="D233" t="inlineStr"/>
       <c r="E233" t="inlineStr"/>
       <c r="F233" t="n">
-        <v>1.313333333333333</v>
+        <v>2.196666666666667</v>
       </c>
       <c r="G233" t="n">
         <v>0</v>
@@ -28168,7 +28168,7 @@
         <v>0</v>
       </c>
       <c r="Q233" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="R233" t="n">
         <v>0.08</v>
@@ -28496,7 +28496,7 @@
       <c r="D236" t="inlineStr"/>
       <c r="E236" t="inlineStr"/>
       <c r="F236" t="n">
-        <v>0.7721518987341772</v>
+        <v>1.10126582278481</v>
       </c>
       <c r="G236" t="n">
         <v>0</v>
@@ -28525,7 +28525,7 @@
         <v>0</v>
       </c>
       <c r="Q236" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="R236" t="n">
         <v>0.089</v>
@@ -28573,22 +28573,22 @@
         <v>0.01730769230769231</v>
       </c>
       <c r="AG236" t="n">
-        <v>0.09754098360655739</v>
+        <v>0.09754098360655737</v>
       </c>
       <c r="AH236" t="n">
-        <v>0.09754098360655739</v>
+        <v>0.09754098360655737</v>
       </c>
       <c r="AI236" t="n">
-        <v>0.09754098360655739</v>
+        <v>0.09754098360655737</v>
       </c>
       <c r="AJ236" t="n">
-        <v>0.09754098360655739</v>
+        <v>0.09754098360655737</v>
       </c>
       <c r="AK236" t="n">
-        <v>0.09754098360655739</v>
+        <v>0.09754098360655737</v>
       </c>
       <c r="AL236" t="n">
-        <v>0.09754098360655739</v>
+        <v>0.09754098360655737</v>
       </c>
       <c r="AM236" t="n">
         <v>0.01730769230769231</v>
@@ -28734,7 +28734,7 @@
       <c r="D238" t="inlineStr"/>
       <c r="E238" t="inlineStr"/>
       <c r="F238" t="n">
-        <v>0.4114285714285714</v>
+        <v>0.8228571428571428</v>
       </c>
       <c r="G238" t="n">
         <v>0</v>
@@ -28763,7 +28763,7 @@
         <v>0</v>
       </c>
       <c r="Q238" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R238" t="n">
         <v>0.089</v>
